--- a/duty_roster/output/2026-10/Schedule_2026-10.xlsx
+++ b/duty_roster/output/2026-10/Schedule_2026-10.xlsx
@@ -36,7 +36,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,18 @@
         <bgColor rgb="00B1A0C7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
+        <bgColor rgb="0092D050"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -254,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -301,28 +313,52 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -983,66 +1019,106 @@
       <c r="H6" s="11" t="n"/>
       <c r="I6" s="11" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>NICU</t>
         </is>
       </c>
-      <c r="N6" s="11" t="n"/>
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
       <c r="O6" s="13" t="inlineStr">
         <is>
           <t>大曲厚生</t>
         </is>
       </c>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="14" t="n"/>
-      <c r="R6" s="14" t="n"/>
-      <c r="S6" s="15" t="n"/>
-      <c r="T6" s="14" t="n"/>
-      <c r="U6" s="14" t="n"/>
-      <c r="V6" s="16" t="inlineStr">
+      <c r="P6" s="17" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="Q6" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="17" t="n"/>
+      <c r="T6" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="U6" s="18" t="n"/>
+      <c r="V6" s="17" t="inlineStr">
         <is>
           <t>NICU</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>佐々木</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="19" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="19" t="n"/>
-      <c r="H7" s="18" t="n"/>
-      <c r="I7" s="18" t="n"/>
-      <c r="J7" s="19" t="n"/>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="18" t="n"/>
-      <c r="M7" s="19" t="n"/>
-      <c r="N7" s="18" t="n"/>
-      <c r="O7" s="18" t="n"/>
-      <c r="P7" s="20" t="inlineStr">
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="23" t="n"/>
+      <c r="N7" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="O7" s="24" t="n"/>
+      <c r="P7" s="25" t="inlineStr">
         <is>
           <t>市立救急</t>
         </is>
       </c>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>保育園行事</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="23" t="n"/>
-      <c r="U7" s="23" t="n"/>
-      <c r="V7" s="22" t="n"/>
+      <c r="Q7" s="26" t="inlineStr">
+        <is>
+          <t>私用</t>
+        </is>
+      </c>
+      <c r="R7" s="26" t="n"/>
+      <c r="S7" s="23" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="n"/>
+      <c r="V7" s="23" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1206,7 +1282,7 @@
         </is>
       </c>
       <c r="C10" s="13" t="n"/>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>県医師会</t>
         </is>
@@ -1253,10 +1329,10 @@
         </is>
       </c>
       <c r="R10" s="13" t="n"/>
-      <c r="S10" s="16" t="n"/>
+      <c r="S10" s="27" t="n"/>
       <c r="T10" s="13" t="n"/>
       <c r="U10" s="13" t="n"/>
-      <c r="V10" s="16" t="n"/>
+      <c r="V10" s="27" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -1264,87 +1340,143 @@
           <t>仲本</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
           <t>秋田厚生</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n"/>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
           <t>外来</t>
         </is>
       </c>
       <c r="F11" s="13" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>心臓カテーテル</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="11" t="n"/>
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="17" t="n"/>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
       <c r="O11" s="13" t="inlineStr">
         <is>
           <t>由利組合</t>
         </is>
       </c>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="14" t="n"/>
-      <c r="R11" s="14" t="n"/>
-      <c r="S11" s="15" t="n"/>
-      <c r="T11" s="14" t="n"/>
-      <c r="U11" s="14" t="n"/>
-      <c r="V11" s="15" t="n"/>
+      <c r="P11" s="17" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="Q11" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="R11" s="18" t="n"/>
+      <c r="S11" s="28" t="n"/>
+      <c r="T11" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="U11" s="18" t="n"/>
+      <c r="V11" s="28" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>佐々木</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>大森</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t>心臓カテーテル</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="18" t="n"/>
-      <c r="L12" s="18" t="n"/>
-      <c r="M12" s="19" t="n"/>
-      <c r="N12" s="18" t="n"/>
-      <c r="O12" s="18" t="n"/>
-      <c r="P12" s="20" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="29" t="n"/>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="n"/>
+      <c r="J12" s="29" t="n"/>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="23" t="n"/>
+      <c r="N12" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="O12" s="24" t="n"/>
+      <c r="P12" s="25" t="inlineStr">
         <is>
           <t>市立救急</t>
         </is>
       </c>
-      <c r="Q12" s="23" t="n"/>
-      <c r="R12" s="23" t="n"/>
-      <c r="S12" s="22" t="n"/>
-      <c r="T12" s="21" t="inlineStr">
+      <c r="Q12" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="R12" s="24" t="n"/>
+      <c r="S12" s="29" t="n"/>
+      <c r="T12" s="24" t="inlineStr">
         <is>
           <t>NICU</t>
         </is>
       </c>
-      <c r="U12" s="21" t="n"/>
-      <c r="V12" s="22" t="n"/>
+      <c r="U12" s="24" t="n"/>
+      <c r="V12" s="29" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1537,7 +1669,7 @@
           <t>1ヶ月健診</t>
         </is>
       </c>
-      <c r="M15" s="16" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t>医学教育MT</t>
         </is>
@@ -1559,10 +1691,10 @@
         </is>
       </c>
       <c r="R15" s="13" t="n"/>
-      <c r="S15" s="16" t="n"/>
+      <c r="S15" s="27" t="n"/>
       <c r="T15" s="13" t="n"/>
       <c r="U15" s="13" t="n"/>
-      <c r="V15" s="16" t="n"/>
+      <c r="V15" s="27" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
@@ -1570,33 +1702,49 @@
           <t>仲本</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>外来</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="11" t="n"/>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
           <t>能代厚生</t>
         </is>
       </c>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="11" t="n"/>
-      <c r="L16" s="11" t="n"/>
-      <c r="M16" s="16" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="17" t="inlineStr">
         <is>
           <t>NICU</t>
         </is>
       </c>
-      <c r="N16" s="13" t="inlineStr">
-        <is>
-          <t>雄勝</t>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
         </is>
       </c>
       <c r="O16" s="13" t="inlineStr">
@@ -1604,73 +1752,85 @@
           <t>大曲厚生</t>
         </is>
       </c>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="13" t="inlineStr">
+      <c r="P16" s="17" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="Q16" s="16" t="inlineStr">
         <is>
           <t>小児科</t>
         </is>
       </c>
-      <c r="R16" s="13" t="n"/>
-      <c r="S16" s="15" t="n"/>
-      <c r="T16" s="14" t="n"/>
-      <c r="U16" s="14" t="n"/>
-      <c r="V16" s="15" t="n"/>
+      <c r="R16" s="16" t="n"/>
+      <c r="S16" s="17" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="T16" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="U16" s="16" t="n"/>
+      <c r="V16" s="17" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>佐々木</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>夏季休暇</t>
         </is>
       </c>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>夏季休暇</t>
         </is>
       </c>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="19" t="n"/>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="F17" s="26" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="26" t="inlineStr">
         <is>
           <t>夏季休暇</t>
         </is>
       </c>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="19" t="n"/>
-      <c r="K17" s="21" t="inlineStr">
+      <c r="I17" s="26" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="26" t="inlineStr">
         <is>
           <t>夏季休暇</t>
         </is>
       </c>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="19" t="n"/>
-      <c r="N17" s="21" t="inlineStr">
+      <c r="L17" s="26" t="n"/>
+      <c r="M17" s="25" t="n"/>
+      <c r="N17" s="26" t="inlineStr">
         <is>
           <t>夏季休暇</t>
         </is>
       </c>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="19" t="n"/>
-      <c r="Q17" s="21" t="inlineStr">
+      <c r="O17" s="26" t="n"/>
+      <c r="P17" s="25" t="n"/>
+      <c r="Q17" s="26" t="inlineStr">
         <is>
           <t>夏季休暇</t>
         </is>
       </c>
-      <c r="R17" s="21" t="n"/>
-      <c r="S17" s="22" t="n"/>
-      <c r="T17" s="21" t="inlineStr">
+      <c r="R17" s="26" t="n"/>
+      <c r="S17" s="25" t="n"/>
+      <c r="T17" s="26" t="inlineStr">
         <is>
           <t>夏季休暇</t>
         </is>
       </c>
-      <c r="U17" s="21" t="n"/>
-      <c r="V17" s="22" t="n"/>
+      <c r="U17" s="26" t="n"/>
+      <c r="V17" s="25" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1845,16 +2005,12 @@
         </is>
       </c>
       <c r="F20" s="13" t="n"/>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G20" s="27" t="inlineStr">
         <is>
           <t>研究班MT</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>心臓カテーテル</t>
-        </is>
-      </c>
+      <c r="H20" s="11" t="n"/>
       <c r="I20" s="13" t="inlineStr">
         <is>
           <t>日赤</t>
@@ -1896,95 +2052,155 @@
           <t>仲本</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="12" t="n"/>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="n"/>
       <c r="E21" s="13" t="inlineStr">
         <is>
           <t>外来</t>
         </is>
       </c>
       <c r="F21" s="13" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>心臓カテーテル</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="12" t="n"/>
-      <c r="K21" s="11" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="16" t="inlineStr">
+      <c r="G21" s="28" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>雄勝(仮)</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="n"/>
+      <c r="M21" s="17" t="inlineStr">
         <is>
           <t>NICU</t>
         </is>
       </c>
-      <c r="N21" s="11" t="n"/>
+      <c r="N21" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
       <c r="O21" s="13" t="inlineStr">
         <is>
           <t>能代厚生</t>
         </is>
       </c>
-      <c r="P21" s="12" t="n"/>
-      <c r="Q21" s="14" t="n"/>
-      <c r="R21" s="14" t="n"/>
-      <c r="S21" s="15" t="n"/>
-      <c r="T21" s="14" t="n"/>
-      <c r="U21" s="14" t="n"/>
-      <c r="V21" s="16" t="inlineStr">
+      <c r="P21" s="28" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="Q21" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="R21" s="16" t="n"/>
+      <c r="S21" s="17" t="n"/>
+      <c r="T21" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="U21" s="18" t="n"/>
+      <c r="V21" s="17" t="inlineStr">
         <is>
           <t>NICU</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>佐々木</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="19" t="n"/>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>心臓カテーテル</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="n"/>
-      <c r="J22" s="19" t="n"/>
-      <c r="K22" s="18" t="n"/>
-      <c r="L22" s="18" t="n"/>
-      <c r="M22" s="19" t="n"/>
-      <c r="N22" s="18" t="n"/>
-      <c r="O22" s="18" t="n"/>
-      <c r="P22" s="20" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="n"/>
+      <c r="J22" s="29" t="n"/>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="n"/>
+      <c r="M22" s="23" t="n"/>
+      <c r="N22" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="O22" s="24" t="n"/>
+      <c r="P22" s="29" t="inlineStr">
         <is>
           <t>NICU</t>
         </is>
       </c>
-      <c r="Q22" s="23" t="n"/>
-      <c r="R22" s="23" t="n"/>
-      <c r="S22" s="22" t="n"/>
-      <c r="T22" s="21" t="inlineStr">
+      <c r="Q22" s="22" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="R22" s="22" t="n"/>
+      <c r="S22" s="23" t="n"/>
+      <c r="T22" s="24" t="inlineStr">
         <is>
           <t>NICU</t>
         </is>
       </c>
-      <c r="U22" s="21" t="n"/>
-      <c r="V22" s="22" t="n"/>
+      <c r="U22" s="24" t="n"/>
+      <c r="V22" s="23" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -2158,11 +2374,7 @@
       </c>
       <c r="F25" s="13" t="n"/>
       <c r="G25" s="12" t="n"/>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>心臓カテーテル</t>
-        </is>
-      </c>
+      <c r="H25" s="11" t="n"/>
       <c r="I25" s="13" t="inlineStr">
         <is>
           <t>高校訪問</t>
@@ -2208,13 +2420,21 @@
           <t>仲本</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n"/>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
           <t>北秋田</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n"/>
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
           <t>療育</t>
@@ -2225,131 +2445,205 @@
           <t>外来</t>
         </is>
       </c>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>心臓カテーテル</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="11" t="n"/>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="11" t="n"/>
-      <c r="O26" s="11" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="14" t="n"/>
-      <c r="R26" s="14" t="n"/>
-      <c r="S26" s="15" t="n"/>
+      <c r="G26" s="28" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I26" s="16" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="L26" s="18" t="n"/>
+      <c r="M26" s="28" t="n"/>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="O26" s="16" t="n"/>
+      <c r="P26" s="17" t="n"/>
+      <c r="Q26" s="18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="R26" s="18" t="n"/>
+      <c r="S26" s="28" t="n"/>
       <c r="T26" s="14" t="n"/>
       <c r="U26" s="14" t="n"/>
       <c r="V26" s="15" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>佐々木</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>大森</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="18" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>心臓カテーテル</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="18" t="n"/>
-      <c r="L27" s="18" t="n"/>
-      <c r="M27" s="19" t="n"/>
-      <c r="N27" s="21" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="L27" s="24" t="n"/>
+      <c r="M27" s="29" t="n"/>
+      <c r="N27" s="22" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="O27" s="22" t="n"/>
+      <c r="P27" s="25" t="inlineStr">
         <is>
           <t>レクチャー</t>
         </is>
       </c>
-      <c r="O27" s="21" t="n"/>
-      <c r="P27" s="19" t="n"/>
-      <c r="Q27" s="23" t="n"/>
-      <c r="R27" s="23" t="n"/>
-      <c r="S27" s="22" t="n"/>
-      <c r="T27" s="23" t="n"/>
-      <c r="U27" s="23" t="n"/>
-      <c r="V27" s="22" t="n"/>
+      <c r="Q27" s="24" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="R27" s="24" t="n"/>
+      <c r="S27" s="29" t="n"/>
+      <c r="T27" s="30" t="n"/>
+      <c r="U27" s="30" t="n"/>
+      <c r="V27" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="65">
-    <mergeCell ref="Q16:R16"/>
+  <mergeCells count="103">
     <mergeCell ref="Q14:S14"/>
     <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="B14:D14"/>
     <mergeCell ref="N2:P2"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="T9:V9"/>
     <mergeCell ref="Q10:V10"/>
     <mergeCell ref="H10:I10"/>
-    <mergeCell ref="N14:P14"/>
     <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="H2:J2"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B1:V1"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="Q6:S6"/>
     <mergeCell ref="T2:V2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="K21:L21"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="Q15:V15"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="Q22:S22"/>
     <mergeCell ref="K14:M14"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="H27:J27"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="K7:M7"/>
     <mergeCell ref="T19:V19"/>
-    <mergeCell ref="H14:J14"/>
     <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="N4:P4"/>
     <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="T24:V24"/>
     <mergeCell ref="E24:G24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="T14:V14"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="K9:M9"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="H4:J4"/>
-    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="T6:U6"/>
     <mergeCell ref="E4:G4"/>
     <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="T9:V9"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="B1:V1"/>
+    <mergeCell ref="T11:V11"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="Q15:V15"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="T24:V24"/>
     <mergeCell ref="N27:O27"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E21:F21"/>
